--- a/outputs/reports/AZZAM_EVERGREEN_PLAN.xlsx
+++ b/outputs/reports/AZZAM_EVERGREEN_PLAN.xlsx
@@ -1356,12 +1356,12 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>I’ve been seriously considering deleting all my trading apps. After 8 months of studying charts, buying courses, and trying to learn the markets, I’m still losing money overall. It</t>
+          <t xml:space="preserve">Just did a backtest on this strategy between Feb-23 to half of Aug-23 and only using the 2022 ICT entry model on the retracement to FVG after MSS. Took 50% off at 50% to TP at the </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JXHrTloZ-nE</t>
+          <t>https://www.youtube.com/watch?v=o0v4KQxZbpU</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>I’ve been seriously considering deleting all my trading apps. After 8 months of studying charts, buying courses, and trying to learn the markets, I’m still losing money overall. It</t>
+          <t xml:space="preserve">Just did a backtest on this strategy between Feb-23 to half of Aug-23 and only using the 2022 ICT entry model on the retracement to FVG after MSS. Took 50% off at 50% to TP at the </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JXHrTloZ-nE</t>
+          <t>https://www.youtube.com/watch?v=o0v4KQxZbpU</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>I’ve been seriously considering deleting all my trading apps. After 8 months of studying charts, buying courses, and trying to learn the markets, I’m still losing money overall. It</t>
+          <t xml:space="preserve">Just did a backtest on this strategy between Feb-23 to half of Aug-23 and only using the 2022 ICT entry model on the retracement to FVG after MSS. Took 50% off at 50% to TP at the </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JXHrTloZ-nE</t>
+          <t>https://www.youtube.com/watch?v=o0v4KQxZbpU</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
